--- a/ci-cd-merge-resolver/repoCollector/datasets/bootique.xlsx
+++ b/ci-cd-merge-resolver/repoCollector/datasets/bootique.xlsx
@@ -71,6 +71,15 @@
     <t>559b27de88d71a5b17500c3022cb96aa90a4bbfc</t>
   </si>
   <si>
+    <t>17794d8f0d4afa1540ba6f583739d5b164036fae</t>
+  </si>
+  <si>
+    <t>b566523108d7887f4194abf2c1b8a6cece95a536</t>
+  </si>
+  <si>
+    <t>c86e617658253d0d307f790490921fe33726a4c1</t>
+  </si>
+  <si>
     <t>005fca1ddeb83439c290c3a0b23f30ffd7c4b92e</t>
   </si>
   <si>
@@ -78,15 +87,6 @@
   </si>
   <si>
     <t>de32d73b7f8755abaabf6a64e15e7c37b9a7f001</t>
-  </si>
-  <si>
-    <t>17794d8f0d4afa1540ba6f583739d5b164036fae</t>
-  </si>
-  <si>
-    <t>b566523108d7887f4194abf2c1b8a6cece95a536</t>
-  </si>
-  <si>
-    <t>c86e617658253d0d307f790490921fe33726a4c1</t>
   </si>
 </sst>
 </file>
@@ -177,7 +177,7 @@
         <v>12</v>
       </c>
       <c r="D2" t="n" s="0">
-        <v>93.0</v>
+        <v>174.0</v>
       </c>
       <c r="E2" t="n" s="0">
         <v>2.0</v>
@@ -192,10 +192,10 @@
         <v>1</v>
       </c>
       <c r="I2" t="n" s="0">
-        <v>0.7860000729560852</v>
+        <v>0.7589999437332153</v>
       </c>
       <c r="J2" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -209,7 +209,7 @@
         <v>15</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>93.0</v>
+        <v>174.0</v>
       </c>
       <c r="E3" t="n" s="0">
         <v>6.0</v>
@@ -224,10 +224,10 @@
         <v>1</v>
       </c>
       <c r="I3" t="n" s="0">
-        <v>0.8580000996589661</v>
+        <v>0.578000009059906</v>
       </c>
       <c r="J3" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -241,7 +241,7 @@
         <v>18</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>228.0</v>
+        <v>230.0</v>
       </c>
       <c r="E4" t="n" s="0">
         <v>2.0</v>
@@ -256,10 +256,10 @@
         <v>1</v>
       </c>
       <c r="I4" t="n" s="0">
-        <v>2.144000291824341</v>
+        <v>1.4779999256134033</v>
       </c>
       <c r="J4" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -273,7 +273,7 @@
         <v>21</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>95.0</v>
+        <v>174.0</v>
       </c>
       <c r="E5" t="n" s="0">
         <v>1.0</v>
@@ -288,10 +288,10 @@
         <v>1</v>
       </c>
       <c r="I5" t="n" s="0">
-        <v>0.8730000257492065</v>
+        <v>0.6399999260902405</v>
       </c>
       <c r="J5" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -305,7 +305,7 @@
         <v>24</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>95.0</v>
+        <v>174.0</v>
       </c>
       <c r="E6" t="n" s="0">
         <v>1.0</v>
@@ -320,10 +320,10 @@
         <v>1</v>
       </c>
       <c r="I6" t="n" s="0">
-        <v>0.921999990940094</v>
+        <v>0.304999977350235</v>
       </c>
       <c r="J6" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
